--- a/business_surveys/022_social_media_engagement_metrics_report_form--business_surveys.xlsx
+++ b/business_surveys/022_social_media_engagement_metrics_report_form--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Facebook'}</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Instagram'}</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'linkedin'}</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'LinkedIn'}</t>
+          <t>LinkedIn</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'twitter'}</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Twitter'}</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'hourly'}</t>
+          <t>hourly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Hourly'}</t>
+          <t>Hourly</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'posts'}</t>
+          <t>posts</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Posts'}</t>
+          <t>Posts</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'stories'}</t>
+          <t>stories</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Stories'}</t>
+          <t>Stories</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'live_streaming'}</t>
+          <t>live_streaming</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Live Streaming'}</t>
+          <t>Live Streaming</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'post_reach'}</t>
+          <t>post_reach</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Post Reach'}</t>
+          <t>Post Reach</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'engagement_rate'}</t>
+          <t>engagement_rate</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Engagement Rate'}</t>
+          <t>Engagement Rate</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'comment_count'}</t>
+          <t>comment_count</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Comment Count'}</t>
+          <t>Comment Count</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'post_click-through_rate'}</t>
+          <t>post_click-through_rate</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Post Click-Through Rate'}</t>
+          <t>Post Click-Through Rate</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'sentiment_analysis'}</t>
+          <t>sentiment_analysis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Sentiment Analysis'}</t>
+          <t>Sentiment Analysis</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'audience_growth_rate'}</t>
+          <t>audience_growth_rate</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Audience Growth Rate'}</t>
+          <t>Audience Growth Rate</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'top-engagement_content'}</t>
+          <t>top-engagement_content</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Top-Engagement Content'}</t>
+          <t>Top-Engagement Content</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'hashtags_used'}</t>
+          <t>hashtags_used</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'Hashtags Used'}</t>
+          <t>Hashtags Used</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'engagement_index'}</t>
+          <t>engagement_index</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'Engagement Index'}</t>
+          <t>Engagement Index</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'week'}</t>
+          <t>week</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Week'}</t>
+          <t>Week</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'month'}</t>
+          <t>month</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Month'}</t>
+          <t>Month</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'quarter'}</t>
+          <t>quarter</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Quarter'}</t>
+          <t>Quarter</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'year'}</t>
+          <t>year</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Year'}</t>
+          <t>Year</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'total'}</t>
+          <t>total</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Total'}</t>
+          <t>Total</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pdf'}</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'PDF'}</t>
+          <t>PDF</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'csv'}</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'CSV'}</t>
+          <t>CSV</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'json'}</t>
+          <t>json</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'JSON'}</t>
+          <t>JSON</t>
         </is>
       </c>
     </row>
